--- a/public/TemplateExcel/Lecturer.xlsx
+++ b/public/TemplateExcel/Lecturer.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/38f9fe7ab19c9b08/Máy tính/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAn\EduAttend\fe\public\TemplateExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC1048AC099B6E205BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9572478-576F-458A-B2F2-79B458231A82}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C33058-424A-4B14-AB24-911F79CC6866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>Email</t>
   </si>
   <si>
-    <t>SDT</t>
-  </si>
-  <si>
     <t>Mã Khoa</t>
   </si>
   <si>
@@ -76,6 +73,9 @@
   </si>
   <si>
     <t>0900000002</t>
+  </si>
+  <si>
+    <t>SDT(Có thể bỏ trống)</t>
   </si>
 </sst>
 </file>
@@ -113,7 +113,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,15 +121,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -146,10 +162,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -419,68 +431,69 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
+      <c r="F1" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
